--- a/evaluacion-gestion-riesgos/Consolidado_Evaluacion_Gestion_Riesgos.xlsx
+++ b/evaluacion-gestion-riesgos/Consolidado_Evaluacion_Gestion_Riesgos.xlsx
@@ -336,6 +336,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -450,10 +451,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="2"/>
                 <pt idx="0">
-                  <v>146</v>
+                  <v>154</v>
                 </pt>
                 <pt idx="1">
-                  <v>145</v>
+                  <v>137</v>
                 </pt>
               </numCache>
             </numRef>
@@ -474,6 +475,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -549,9 +551,9 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>'Consolidado por Gerencia'!$A$5:$A$14</f>
+              <f>'Consolidado por Gerencia'!$A$5:$A$13</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>Auditoría Interna</v>
                 </pt>
@@ -571,15 +573,12 @@
                   <v>Gerencia de Negocios</v>
                 </pt>
                 <pt idx="6">
-                  <v>Gerencia de Negocios (Agencias)</v>
+                  <v>Gerencia de Oficialía de Cumplimiento</v>
                 </pt>
                 <pt idx="7">
-                  <v>Gerencia de Oficialía de Cumplimiento</v>
+                  <v>Gerencia de Operaciones</v>
                 </pt>
                 <pt idx="8">
-                  <v>Gerencia de Operaciones</v>
-                </pt>
-                <pt idx="9">
                   <v>Gerencia de Sistemas</v>
                 </pt>
               </strCache>
@@ -587,18 +586,18 @@
           </cat>
           <val>
             <numRef>
-              <f>'Consolidado por Gerencia'!$C$5:$C$14</f>
+              <f>'Consolidado por Gerencia'!$C$5:$C$13</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>5</v>
                 </pt>
                 <pt idx="1">
-                  <v>27</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="2">
-                  <v>14</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="3">
                   <v>3</v>
@@ -607,18 +606,15 @@
                   <v>8</v>
                 </pt>
                 <pt idx="5">
-                  <v>23</v>
+                  <v>65</v>
                 </pt>
                 <pt idx="6">
-                  <v>34</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="7">
-                  <v>7</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="8">
-                  <v>8</v>
-                </pt>
-                <pt idx="9">
                   <v>17</v>
                 </pt>
               </numCache>
@@ -680,9 +676,9 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>'Consolidado por Gerencia'!$A$5:$A$14</f>
+              <f>'Consolidado por Gerencia'!$A$5:$A$13</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>Auditoría Interna</v>
                 </pt>
@@ -702,15 +698,12 @@
                   <v>Gerencia de Negocios</v>
                 </pt>
                 <pt idx="6">
-                  <v>Gerencia de Negocios (Agencias)</v>
+                  <v>Gerencia de Oficialía de Cumplimiento</v>
                 </pt>
                 <pt idx="7">
-                  <v>Gerencia de Oficialía de Cumplimiento</v>
+                  <v>Gerencia de Operaciones</v>
                 </pt>
                 <pt idx="8">
-                  <v>Gerencia de Operaciones</v>
-                </pt>
-                <pt idx="9">
                   <v>Gerencia de Sistemas</v>
                 </pt>
               </strCache>
@@ -718,18 +711,18 @@
           </cat>
           <val>
             <numRef>
-              <f>'Consolidado por Gerencia'!$D$5:$D$14</f>
+              <f>'Consolidado por Gerencia'!$D$5:$D$13</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>2</v>
                 </pt>
                 <pt idx="1">
-                  <v>5</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="2">
-                  <v>7</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="3">
                   <v>6</v>
@@ -738,18 +731,15 @@
                   <v>10</v>
                 </pt>
                 <pt idx="5">
-                  <v>38</v>
+                  <v>101</v>
                 </pt>
                 <pt idx="6">
-                  <v>63</v>
+                  <v>0</v>
                 </pt>
                 <pt idx="7">
-                  <v>0</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="8">
-                  <v>8</v>
-                </pt>
-                <pt idx="9">
                   <v>6</v>
                 </pt>
               </numCache>
@@ -877,6 +867,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1097,16 +1088,16 @@
                   <v>1</v>
                 </pt>
                 <pt idx="1">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="2">
                   <v>2</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="4">
-                  <v>1</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="5">
                   <v>5</v>
@@ -1130,7 +1121,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="12">
-                  <v>0</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="13">
                   <v>4</v>
@@ -1181,7 +1172,7 @@
                   <v>16</v>
                 </pt>
                 <pt idx="29">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="30">
                   <v>2</v>
@@ -1208,7 +1199,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="38">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="39">
                   <v>1</v>
@@ -1426,16 +1417,16 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>1</v>
+                  <v>0</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
                 </pt>
                 <pt idx="3">
-                  <v>13</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="4">
-                  <v>11</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="5">
                   <v>11</v>
@@ -1459,7 +1450,7 @@
                   <v>3</v>
                 </pt>
                 <pt idx="12">
-                  <v>2</v>
+                  <v>0</v>
                 </pt>
                 <pt idx="13">
                   <v>4</v>
@@ -1510,7 +1501,7 @@
                   <v>1</v>
                 </pt>
                 <pt idx="29">
-                  <v>8</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="30">
                   <v>1</v>
@@ -1537,7 +1528,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="38">
-                  <v>2</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="39">
                   <v>0</v>
@@ -8462,7 +8453,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8490,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8527,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8564,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8601,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8638,7 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8675,7 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8712,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9008,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9045,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9082,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9119,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9156,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9193,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9230,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9267,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9304,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9341,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9378,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9415,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9452,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9489,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9526,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9563,7 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9600,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9637,7 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9674,7 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9711,7 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9748,7 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9785,7 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9822,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9859,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9896,7 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9933,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9970,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10007,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10044,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10081,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10118,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10155,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10192,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10229,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10266,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10303,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10340,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10377,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10414,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10451,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10488,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10525,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10571,7 +10562,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10599,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10636,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10673,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10710,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10747,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10784,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10821,7 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10858,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10895,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10932,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10969,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11015,7 +11006,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11043,7 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11080,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11117,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11154,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11191,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11228,7 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11265,7 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11302,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11339,7 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11376,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11413,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11450,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11487,7 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11524,7 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11561,7 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11598,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11635,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11681,7 +11672,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11709,7 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11746,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11783,7 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11820,7 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11857,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11894,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11931,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11968,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12005,7 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12042,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12079,7 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12116,7 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12153,7 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12190,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12227,7 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12264,7 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12301,7 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12347,7 +12338,7 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12375,7 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12421,7 +12412,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12449,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12486,7 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12523,7 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12560,7 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -13405,7 +13396,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -13571,22 +13561,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO ALEXANDER  ALFARO ARGUETA </t>
+          <t xml:space="preserve">NELSON ULISES CAMPOS FLORES </t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>977</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
+          <t>GERENCIA GENERAL</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,125 +13588,125 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIEL FRANCISCO MOLINA DIAZ </t>
+          <t xml:space="preserve">ANDREA RAQUEL MONTOYA ALARCON </t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>814</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>AUXILIAR JURIDICO DE ESCRITURACION</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
+          <t>DEPARTAMENTO LEGAL</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia Legal y Cumplimiento Normativo</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALEXANDER ABREGO </t>
+          <t xml:space="preserve">CARLOS RENE CASTILLO GAMEZ </t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>592</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>ASISTENTE TECNICO LEGAL</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
+          <t>DEPARTAMENTO LEGAL</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia Legal y Cumplimiento Normativo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ALBERTO MEJIA DELGADO </t>
+          <t xml:space="preserve">CHRISTIAN ENRIQUE CAMPOS PRIVADO </t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>905</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>ASISTENTE TECNICO LEGAL</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
+          <t>DEPARTAMENTO LEGAL</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia Legal y Cumplimiento Normativo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NELSON ULISES CAMPOS FLORES </t>
+          <t xml:space="preserve">DANIELA MARIA FUENTES MEDINA </t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>843</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>AUXILIAR JURIDICO DE CONTRATACION</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>GERENCIA GENERAL</t>
+          <t>DEPARTAMENTO LEGAL</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia Legal y Cumplimiento Normativo</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA RAQUEL MONTOYA ALARCON </t>
+          <t xml:space="preserve">JUAN JOSE CAÑAS COMAYAGUA </t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>442</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR JURIDICO DE ESCRITURACION</t>
+          <t>JEFE DE DEPARTAMENTO LEGAL</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -13733,17 +13723,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS RENE CASTILLO GAMEZ </t>
+          <t xml:space="preserve">NICOLLE ALEXANDRA MARINERO GALLARDO </t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>831</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO LEGAL</t>
+          <t>AUXILIAR JURIDICO NOTARIAL</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -13760,125 +13750,125 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHRISTIAN ENRIQUE CAMPOS PRIVADO </t>
+          <t xml:space="preserve">CLAUDIA MARLENE CABRERA SANCHEZ </t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO LEGAL</t>
+          <t>SUPERVISOR DE CONTABILIDAD</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO LEGAL</t>
+          <t>DEPARTAMENTO DE CONTABILIDAD</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Gerencia Legal y Cumplimiento Normativo</t>
+          <t>Gerencia de Finanzas y Planificación</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA MARIA FUENTES MEDINA </t>
+          <t>JENNIFER MARCELA MORALES  TORRES</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>749</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR JURIDICO DE CONTRATACION</t>
+          <t>CONTADOR BANCARIO</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO LEGAL</t>
+          <t>DEPARTAMENTO DE CONTABILIDAD</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Gerencia Legal y Cumplimiento Normativo</t>
+          <t>Gerencia de Finanzas y Planificación</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN JOSE CAÑAS COMAYAGUA </t>
+          <t xml:space="preserve">JORDAN ALEXANDER FLORES HERRERA </t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>916</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE DEPARTAMENTO LEGAL</t>
+          <t>AUXILIAR CONTABLE DE DIGITALIZACION</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO LEGAL</t>
+          <t>DEPARTAMENTO DE CONTABILIDAD</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Gerencia Legal y Cumplimiento Normativo</t>
+          <t>Gerencia de Finanzas y Planificación</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLLE ALEXANDRA MARINERO GALLARDO </t>
+          <t xml:space="preserve">MILAGRO TRINIDAD ROMERO MONTERROSA </t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>571</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR JURIDICO NOTARIAL</t>
+          <t>ASISTENTE TECNICO DE IMPUESTOS</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO LEGAL</t>
+          <t>DEPARTAMENTO DE CONTABILIDAD</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Gerencia Legal y Cumplimiento Normativo</t>
+          <t>Gerencia de Finanzas y Planificación</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLAUDIA MARLENE CABRERA SANCHEZ </t>
+          <t xml:space="preserve">RUBIA ESTELA LEIVA SIBRIAN </t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE CONTABILIDAD</t>
+          <t>ASISTENTE TECNICO DE PAGOS</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -13895,17 +13885,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>JENNIFER MARCELA MORALES  TORRES</t>
+          <t xml:space="preserve">THELMA JUDITH QUINTANILLA VALLE </t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>CONTADOR BANCARIO</t>
+          <t>AUXILIAR CONTABLE DE DIGITALIZACION</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -13922,22 +13912,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORDAN ALEXANDER FLORES HERRERA </t>
+          <t xml:space="preserve">EFRAIN ANTONIO  AYALA LOPEZ  </t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>946</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR CONTABLE DE DIGITALIZACION</t>
+          <t>JEFE DE PLANIFICACION Y ANALISIS</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE CONTABILIDAD</t>
+          <t>DEPARTAMENTO DE PLANIFICACIÓN Y ANALISIS</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13949,22 +13939,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILAGRO TRINIDAD ROMERO MONTERROSA </t>
+          <t xml:space="preserve">ESTER ALEYDA GODOY CAMPOS </t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO DE IMPUESTOS</t>
+          <t>ASISTENTE TECNICO DE PLANIFICACION</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE CONTABILIDAD</t>
+          <t>DEPARTAMENTO DE PLANIFICACIÓN Y ANALISIS</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13976,22 +13966,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBIA ESTELA LEIVA SIBRIAN </t>
+          <t xml:space="preserve">RAFAEL ANDRES MARAVILLA GUERRA </t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>839</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO DE PAGOS</t>
+          <t>ASISTENTE DE ANALISIS Y NORMATIVAS</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE CONTABILIDAD</t>
+          <t>DEPARTAMENTO DE PLANIFICACIÓN Y ANALISIS</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14003,22 +13993,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">THELMA JUDITH QUINTANILLA VALLE </t>
+          <t xml:space="preserve">PAULA MARIA CALDERON PEREZ </t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>942</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR CONTABLE DE DIGITALIZACION</t>
+          <t>ASISTENTE DE GERENCIA DE FINANZAS</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE CONTABILIDAD</t>
+          <t>GERENCIA DE FINANZAS Y PLANIFICACIÓN</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14030,130 +14020,130 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFRAIN ANTONIO  AYALA LOPEZ  </t>
+          <t xml:space="preserve">ANGELA GABRIELA  REYES MOLINA </t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PLANIFICACION Y ANALISIS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE PLANIFICACIÓN Y ANALISIS</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Finanzas y Planificación</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTER ALEYDA GODOY CAMPOS </t>
+          <t xml:space="preserve">BLANCA ARACELY MORENO HERNANDEZ </t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO DE PLANIFICACION</t>
+          <t>AUXILIAR DE OPERACIONES Y ATENCION EN  AGENCIA</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE PLANIFICACIÓN Y ANALISIS</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Finanzas y Planificación</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL ANDRES MARAVILLA GUERRA </t>
+          <t xml:space="preserve">CAROLINA ELIZABETH RAMIREZ PONCE </t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE DE ANALISIS Y NORMATIVAS</t>
+          <t>SUBJEFE DE  AGENCIA</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE PLANIFICACIÓN Y ANALISIS</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Finanzas y Planificación</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULA MARIA CALDERON PEREZ </t>
+          <t xml:space="preserve">ELSY GUADALUPE COREA AGUILUZ </t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE DE GERENCIA DE FINANZAS</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>GERENCIA DE FINANZAS Y PLANIFICACIÓN</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Finanzas y Planificación</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALAN RODRIGO BENITEZ RODRIGUEZ </t>
+          <t xml:space="preserve">ESTHER ABIGAIL FLORES GRANDE </t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>857</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>PASANTE</t>
+          <t>AUXILIAR DE OPERACIONES Y ATENCION EN  AGENCIA</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14165,22 +14155,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMERSON ULISES BELTRAN CORTEZ </t>
+          <t>GRISELDA DEL CARMEN DOMINGUEZ MERINO</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE ATENCION A  ASOCIADOS</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14192,22 +14182,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA ELIZABETH TICAS GOMEZ  </t>
+          <t xml:space="preserve">JAZMIN ABIGAIL VASQUEZ AVELAR </t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>848</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>RECEPCIONISTA</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14219,22 +14209,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>KARLA PATRICIA  ROBLES  CORTEZ</t>
+          <t xml:space="preserve">JOHANA PATRICIA LUNA RAMOS </t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>739</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO DE AFILIACION</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14246,22 +14236,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ANA ESTER ERAZO ORTIZ</t>
+          <t xml:space="preserve">KARLA MERCEDES DELEON DELGADO </t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>440</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE CREDITOS</t>
+          <t xml:space="preserve">JEFE DE AGENCIA  </t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14273,22 +14263,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA VANESSA GARCIA OLIVA </t>
+          <t xml:space="preserve">KATHERINE MICHELLE LOPEZ LOPEZ </t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>768</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE CREDITOS</t>
+          <t>AUXILIAR DE OPERACIONES Y ATENCION EN  AGENCIA</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14300,22 +14290,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>MABEL GERALDINE RAMIREZ PORTILLO</t>
+          <t xml:space="preserve">LEIDY VANESSA GUZMAN SERVELLON  </t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>974</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE ANALISTAS DE CREDITOS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14327,22 +14317,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA LILIAN MENJIVAR GUARDADO </t>
+          <t xml:space="preserve">LETICIA ESMERALDA ROSA </t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE CREDITOS</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
+          <t xml:space="preserve">AGENCIA CENTRAL  </t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14354,22 +14344,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIO LEONEL CANDRAY FLORES </t>
+          <t xml:space="preserve">DORIS ELISA HERNANDEZ </t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>466</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE CREDITOS</t>
+          <t>SERVICIOS VARIOS</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14381,22 +14371,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">YANETH  HERNANDEZ YANES </t>
+          <t>FLOR IMELDA VILLALOBOS ARDON</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE CREDITOS</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14408,22 +14398,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS EDUARDO SERVELLON PEREZ </t>
+          <t xml:space="preserve">GABRIELA CONCEPCION GARCIA GUTIERREZ </t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
+          <t>AUXILIAR DE ATENCION AL ASOCIADO EN AGENCIA</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14435,22 +14425,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>ZULEYMA ALEJANDRA VASQUEZ  MARIN</t>
+          <t xml:space="preserve">JACQUELINE ADRIANA CHAVEZ SARAVIA </t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>811</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14462,22 +14452,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CARMEN MARIA GUTIERREZ ESTRADA</t>
+          <t xml:space="preserve">JAQUELIN JAZMIN ROMERO FLORES </t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>971</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE MERCADEO</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14489,22 +14479,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERARDO ALEXANDER  MARTINEZ RIVERA </t>
+          <t xml:space="preserve">MARTHA ESPERANZA VALTEZ GARCIA </t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>536</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE COMUNICACIONES</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14516,22 +14506,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>IVONNE LISSETH DE JESUS RODRIGUEZ   FLORES</t>
+          <t xml:space="preserve">MERCI ANTONIA CERON MEJIA </t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TELEMARKETING</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14543,22 +14533,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE CARLOS IRENEO HERNANDEZ RODRIGUEZ </t>
+          <t xml:space="preserve">WILBER ERNESTO DIAZ GONZALEZ </t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>890</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE TECNICO DE MERCADEO</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14570,22 +14560,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS FAUSTONY VASQUEZ CIENFUEGOS </t>
+          <t>YANIRA ELIZABETH ORTEGA MIRANDA</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>GESTOR DE DOCUMENTOS</t>
+          <t>SUBJEFE DE  AGENCIA</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
+          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14597,22 +14587,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ALEJANDRA BATRES ALVARADO </t>
+          <t xml:space="preserve">ALFREDO ARMANDO RAMOS ESCOBAR </t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>DISEÑADOR  GRAFICO</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14624,22 +14614,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALEXANDER ROMERO ROMERO </t>
+          <t>ANA MARGARITA SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>GESTOR DE CARTERA DE SEGUROS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14651,22 +14641,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>CLAUDIA MARISOL MADRID BARRIENTOS</t>
+          <t xml:space="preserve">FLOR DE MARIA ROSALES SORTO </t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>873</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>GESTOR DE  RECLAMOS Y SUSCRIPCIONES</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14678,22 +14668,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERIKA VANESSA ALEMAN MIJANGO </t>
+          <t xml:space="preserve">FLOR DEL CARMEN GONZALEZ HERNANDEZ </t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>913</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE VENTA DE SEGUROS</t>
+          <t>SERVICIOS VARIOS</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14705,22 +14695,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JENNYFER AYLIN ESCOBAR ZAMORA </t>
+          <t xml:space="preserve">INGRID PAOLA  CORADO HERNANDEZ </t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>722</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR COMERCIAL DE SEGUROS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14732,22 +14722,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA HAZEL GARCIA COREAS </t>
+          <t xml:space="preserve">JACQUELINE GUADALUPE CEA ALVARADO </t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>933</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE VENTA DE SEGUROS</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14759,22 +14749,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LISSETTE MARICELA SANCHEZ MOLINA </t>
+          <t xml:space="preserve">JULIO ENRIQUE  CAMPOS ANDRADE </t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>624</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE DE SEGUROS</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14786,22 +14776,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBA BEATRIZ MELENDEZ PRUDENCIO </t>
+          <t xml:space="preserve">JULIO RAFAEL FLORES HENRIQUEZ </t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE DE RECUPERACION JUDICIAL Y CARTERA CASTIGADA</t>
+          <t xml:space="preserve">JEFE DE AGENCIA  </t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14813,22 +14803,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA GRISELDA SIGÜENZA MARTINEZ </t>
+          <t xml:space="preserve">STEFFANY MARIELOS MIRO HERNANDEZ </t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>855</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14840,22 +14830,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO HENRIQUEZ RAMIREZ </t>
+          <t xml:space="preserve">YESENIA LISSETH BARAHONA VALLE </t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>891</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
+          <t>AUXILIAR DE ATENCION AL ASOCIADO EN AGENCIA</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14867,22 +14857,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>ROSA ELIZABETH RIVAS AGUILUZ</t>
+          <t>YHANA MILET  VALLE  HERNANDEZ</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>735</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14894,22 +14884,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA GUADALUPE ROQUE SANCHEZ </t>
+          <t>CLELIA DESIREE CAMPOS COSS</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>657</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
+          <t>SERVICIOS VARIOS</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA MERLIOT  </t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14921,22 +14911,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">XOCHILT VERONICA NOUBLEAU </t>
+          <t xml:space="preserve">ERIKA IVETH MANCIA HERNANDEZ </t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -14948,22 +14938,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENIS MARILU ESCOBAR SORTO </t>
+          <t xml:space="preserve">GABRIELA JEANNETTE BOLAÑOS HERRERA </t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>616</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
+          <t>EJECUTIVA DE SEGUROS</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14975,22 +14965,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE HUMBERTO BARILLAS BURGOS </t>
+          <t xml:space="preserve">NANCY CAROLINA FUENTES SORTO </t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>675</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE NEGOCIOS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>GERENCIA DE NEGOCIOS</t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15002,22 +14992,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN CARLOS AGUILAR ASCENCIO </t>
+          <t xml:space="preserve">NORMA ARACELY GUILLEN </t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>CAJERO MOVIL</t>
+          <t>SUBJEFE DE  AGENCIA</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15029,22 +15019,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS FERNANDO MORAN GARCIA </t>
+          <t xml:space="preserve">PAOLA JEANNETTE ROMERO HERNANDEZ  </t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>876</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>JEFE MOVIL DE AGENCIAS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15056,22 +15046,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">REBECA ABIGAIL VEGA FLORES </t>
+          <t xml:space="preserve">ROSARIO DEL CARMEN PEREZ LOPEZ </t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>535</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>CAJERO MOVIL</t>
+          <t xml:space="preserve">JEFE DE AGENCIA  </t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15083,22 +15073,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMUEL ALBERTO SALGUERO RODRIGUEZ </t>
+          <t xml:space="preserve">WALTER ALBERTO BARAHONA DIAZ </t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>748</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>CAJERO MOVIL</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15110,22 +15100,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA VERONICA ACEVEDO BELTRAN </t>
+          <t xml:space="preserve">ZOILA AYDEE LARIOS  </t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASISTENTE PARA CORRESPONSALES FINANCIEROS </t>
+          <t>SERVICIOS VARIOS</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
+          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15137,12 +15127,12 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELA GABRIELA  REYES MOLINA </t>
+          <t xml:space="preserve">SANDRA MARINA  BERRIOS SANTOS </t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>861</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -15152,186 +15142,186 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SAN  MIGUEL  </t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCA ARACELY MORENO HERNANDEZ </t>
+          <t xml:space="preserve">ANA MARIA GIRON </t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE OPERACIONES Y ATENCION EN  AGENCIA</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA ELIZABETH RAMIREZ PONCE </t>
+          <t xml:space="preserve">ANDREA YAMILETH ESCOBAR CHICA </t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>818</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>SUBJEFE DE  AGENCIA</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELSY GUADALUPE COREA AGUILUZ </t>
+          <t xml:space="preserve">GLENDA MARAYA SALAZAR GONZALEZ </t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t xml:space="preserve">JEFE DE AGENCIA  </t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTHER ABIGAIL FLORES GRANDE </t>
+          <t xml:space="preserve">IRVIN ADEMIR PERAZA MOLINA </t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>747</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE OPERACIONES Y ATENCION EN  AGENCIA</t>
+          <t>EJECUTIVO DE SEGUROS</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>GRISELDA DEL CARMEN DOMINGUEZ MERINO</t>
+          <t xml:space="preserve">JEANNETTE ANGELINNE HERNANDEZ MEJIA </t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>SUBJEFE DE  AGENCIA</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAZMIN ABIGAIL VASQUEZ AVELAR </t>
+          <t xml:space="preserve">JOSE CRISTOBAL LOPEZ ESQUIVEL </t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>910</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>MENSAJERO</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHANA PATRICIA LUNA RAMOS </t>
+          <t xml:space="preserve">LUIS GERARDO DUEÑAS VALLE </t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -15341,105 +15331,105 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA MERCEDES DELEON DELGADO </t>
+          <t xml:space="preserve">SOFIA AZMINIA MENA ARGUETA </t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEFE DE AGENCIA  </t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE MICHELLE LOPEZ LOPEZ </t>
+          <t xml:space="preserve">JESSICA YAMILETH LEIVA VASQUEZ </t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>575</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE OPERACIONES Y ATENCION EN  AGENCIA</t>
+          <t>EJECUTIVA DE SEGUROS</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEIDY VANESSA GUZMAN SERVELLON  </t>
+          <t xml:space="preserve">JOSE ALEXANDER TORRES PEREZ </t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>448</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>MENSAJERO</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LETICIA ESMERALDA ROSA </t>
+          <t xml:space="preserve">JOSUE ALEXANDER PEREZ HENRIQUEZ </t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>559</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -15449,132 +15439,132 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA CENTRAL  </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORIS ELISA HERNANDEZ </t>
+          <t xml:space="preserve">KARLA MARCELA  ESCOBAR TRIGUEROS </t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>849</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>SERVICIOS VARIOS</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>FLOR IMELDA VILLALOBOS ARDON</t>
+          <t>MARIA ANGELICA ESCOBAR RENDEROS</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>287</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t xml:space="preserve">JEFE DE AGENCIA  </t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA CONCEPCION GARCIA GUTIERREZ </t>
+          <t xml:space="preserve">MIGUEL ANGEL LEON MENA </t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>755</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE ATENCION AL ASOCIADO EN AGENCIA</t>
+          <t>CAJERO</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACQUELINE ADRIANA CHAVEZ SARAVIA </t>
+          <t xml:space="preserve">XIOMARA BEATRIZ MARTINEZ SERMEÑO </t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>526</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>SUBJEFE DE  AGENCIA</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA SONSONATE  </t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAQUELIN JAZMIN ROMERO FLORES </t>
+          <t xml:space="preserve">EDUARDO JOSE GAMEZ VILLATORO </t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>970</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -15584,51 +15574,51 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA USULUTAN  </t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ESPERANZA VALTEZ GARCIA </t>
+          <t xml:space="preserve">LUIS MANUEL VALENCIA GUERRERO </t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>917</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>SUBJEFE DE  AGENCIA</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA USULUTAN  </t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERCI ANTONIA CERON MEJIA </t>
+          <t xml:space="preserve">MELVIN ELISEO HERNANDEZ MACHADO </t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -15638,1119 +15628,1119 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t xml:space="preserve">AGENCIA USULUTAN  </t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILBER ERNESTO DIAZ GONZALEZ </t>
+          <t xml:space="preserve">ANTONIO ALEXANDER  ALFARO ARGUETA </t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>669</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>YANIRA ELIZABETH ORTEGA MIRANDA</t>
+          <t xml:space="preserve">GABRIEL FRANCISCO MOLINA DIAZ </t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>858</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>SUBJEFE DE  AGENCIA</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLEGIO MEDICO </t>
+          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALFREDO ARMANDO RAMOS ESCOBAR </t>
+          <t xml:space="preserve">JOSE ALEXANDER ABREGO </t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>655</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>ANA MARGARITA SERRANO RUBIO</t>
+          <t xml:space="preserve">LUIS ALBERTO MEJIA DELGADO </t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>835</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>EJECUTIVO DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t>DEPARTAMENTO COMERCIAL DE TARJETA DE CREDITO Y DEBITO</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOR DE MARIA ROSALES SORTO </t>
+          <t xml:space="preserve">ALAN RODRIGO BENITEZ RODRIGUEZ </t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>981</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>PASANTE</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOR DEL CARMEN GONZALEZ HERNANDEZ </t>
+          <t xml:space="preserve">EMERSON ULISES BELTRAN CORTEZ </t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>887</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>SERVICIOS VARIOS</t>
+          <t>AUXILIAR DE ATENCION A  ASOCIADOS</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGRID PAOLA  CORADO HERNANDEZ </t>
+          <t xml:space="preserve">FABIOLA ELIZABETH TICAS GOMEZ  </t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>945</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>RECEPCIONISTA</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACQUELINE GUADALUPE CEA ALVARADO </t>
+          <t>KARLA PATRICIA  ROBLES  CORTEZ</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>744</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>ASISTENTE TECNICO DE AFILIACION</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t>DEPARTAMENTO DE ATENCION A ASOCIADO Y CLIENTE</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIO ENRIQUE  CAMPOS ANDRADE </t>
+          <t>ANA ESTER ERAZO ORTIZ</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>ANALISTA DE CREDITOS</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIO RAFAEL FLORES HENRIQUEZ </t>
+          <t xml:space="preserve">KARLA VANESSA GARCIA OLIVA </t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>809</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEFE DE AGENCIA  </t>
+          <t>ANALISTA DE CREDITOS</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">STEFFANY MARIELOS MIRO HERNANDEZ </t>
+          <t>MABEL GERALDINE RAMIREZ PORTILLO</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>SUPERVISOR DE ANALISTAS DE CREDITOS</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">YESENIA LISSETH BARAHONA VALLE </t>
+          <t xml:space="preserve">MARIA LILIAN MENJIVAR GUARDADO </t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>979</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE ATENCION AL ASOCIADO EN AGENCIA</t>
+          <t>ANALISTA DE CREDITOS</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>YHANA MILET  VALLE  HERNANDEZ</t>
+          <t xml:space="preserve">MARIO LEONEL CANDRAY FLORES </t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>939</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>ANALISTA DE CREDITOS</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA COLONIA MEDICA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>CLELIA DESIREE CAMPOS COSS</t>
+          <t xml:space="preserve">YANETH  HERNANDEZ YANES </t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>730</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>SERVICIOS VARIOS</t>
+          <t>JEFE DE CREDITOS</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA MERLIOT  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE CREDITOS </t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERIKA IVETH MANCIA HERNANDEZ </t>
+          <t xml:space="preserve">CARLOS EDUARDO SERVELLON PEREZ </t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>919</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>AUXILIAR DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t>DEPARTAMENTO DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA JEANNETTE BOLAÑOS HERRERA </t>
+          <t>ZULEYMA ALEJANDRA VASQUEZ  MARIN</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>847</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVA DE SEGUROS</t>
+          <t>JEFE DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t>DEPARTAMENTO DE EDUCACION Y RESPONSABILIDAD SOCIAL</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NANCY CAROLINA FUENTES SORTO </t>
+          <t>CARMEN MARIA GUTIERREZ ESTRADA</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>591</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>JEFE DE MERCADEO</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMA ARACELY GUILLEN </t>
+          <t xml:space="preserve">GERARDO ALEXANDER  MARTINEZ RIVERA </t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>897</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>SUBJEFE DE  AGENCIA</t>
+          <t>ANALISTA DE COMUNICACIONES</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAOLA JEANNETTE ROMERO HERNANDEZ  </t>
+          <t>IVONNE LISSETH DE JESUS RODRIGUEZ   FLORES</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>ASISTENTE TELEMARKETING</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSARIO DEL CARMEN PEREZ LOPEZ </t>
+          <t xml:space="preserve">JOSE CARLOS IRENEO HERNANDEZ RODRIGUEZ </t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEFE DE AGENCIA  </t>
+          <t>ASISTENTE TECNICO DE MERCADEO</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WALTER ALBERTO BARAHONA DIAZ </t>
+          <t xml:space="preserve">LUIS FAUSTONY VASQUEZ CIENFUEGOS </t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>723</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>GESTOR DE DOCUMENTOS</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOILA AYDEE LARIOS  </t>
+          <t xml:space="preserve">MARIA ALEJANDRA BATRES ALVARADO </t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>895</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>SERVICIOS VARIOS</t>
+          <t>DISEÑADOR  GRAFICO</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA PLAZA MUNDO  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE MERCADEO </t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA MARINA  BERRIOS SANTOS </t>
+          <t xml:space="preserve">CARLOS ALEXANDER ROMERO ROMERO </t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>639</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>GESTOR DE CARTERA DE SEGUROS</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SAN  MIGUEL  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA MARIA GIRON </t>
+          <t>CLAUDIA MARISOL MADRID BARRIENTOS</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>544</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>GESTOR DE  RECLAMOS Y SUSCRIPCIONES</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA YAMILETH ESCOBAR CHICA </t>
+          <t xml:space="preserve">ERIKA VANESSA ALEMAN MIJANGO </t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>802</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>EJECUTIVO DE VENTA DE SEGUROS</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLENDA MARAYA SALAZAR GONZALEZ </t>
+          <t xml:space="preserve">JENNYFER AYLIN ESCOBAR ZAMORA </t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>792</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEFE DE AGENCIA  </t>
+          <t>COORDINADOR COMERCIAL DE SEGUROS</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRVIN ADEMIR PERAZA MOLINA </t>
+          <t xml:space="preserve">JUANA HAZEL GARCIA COREAS </t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>805</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE SEGUROS</t>
+          <t>EJECUTIVO DE VENTA DE SEGUROS</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEANNETTE ANGELINNE HERNANDEZ MEJIA </t>
+          <t xml:space="preserve">LISSETTE MARICELA SANCHEZ MOLINA </t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>643</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>SUBJEFE DE  AGENCIA</t>
+          <t>ASISTENTE DE SEGUROS</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t xml:space="preserve">DEPARTAMENTO DE SEGUROS </t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE CRISTOBAL LOPEZ ESQUIVEL </t>
+          <t xml:space="preserve">ALBA BEATRIZ MELENDEZ PRUDENCIO </t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>885</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>MENSAJERO</t>
+          <t>ASISTENTE DE RECUPERACION JUDICIAL Y CARTERA CASTIGADA</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS GERARDO DUEÑAS VALLE </t>
+          <t xml:space="preserve">ANA GRISELDA SIGÜENZA MARTINEZ </t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>528</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>AUXILIAR DE DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOFIA AZMINIA MENA ARGUETA </t>
+          <t xml:space="preserve">JUAN PABLO HENRIQUEZ RAMIREZ </t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>573</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SANTA  ANA  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESSICA YAMILETH LEIVA VASQUEZ </t>
+          <t>ROSA ELIZABETH RIVAS AGUILUZ</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVA DE SEGUROS</t>
+          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALEXANDER TORRES PEREZ </t>
+          <t xml:space="preserve">SANDRA GUADALUPE ROQUE SANCHEZ </t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>MENSAJERO</t>
+          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSUE ALEXANDER PEREZ HENRIQUEZ </t>
+          <t xml:space="preserve">XOCHILT VERONICA NOUBLEAU </t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA MARCELA  ESCOBAR TRIGUEROS </t>
+          <t xml:space="preserve">YENIS MARILU ESCOBAR SORTO </t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>EJECUTIVO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t>DEPARTAMENTO DE SOLUCIONES FINANCIERAS</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>MARIA ANGELICA ESCOBAR RENDEROS</t>
+          <t xml:space="preserve">JOSE HUMBERTO BARILLAS BURGOS </t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>741</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEFE DE AGENCIA  </t>
+          <t>GERENTE DE NEGOCIOS</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t>GERENCIA DE NEGOCIOS</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL LEON MENA </t>
+          <t xml:space="preserve">JUAN CARLOS AGUILAR ASCENCIO </t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>CAJERO MOVIL</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">XIOMARA BEATRIZ MARTINEZ SERMEÑO </t>
+          <t xml:space="preserve">LUIS FERNANDO MORAN GARCIA </t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>651</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>SUBJEFE DE  AGENCIA</t>
+          <t>JEFE MOVIL DE AGENCIAS</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA SONSONATE  </t>
+          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO JOSE GAMEZ VILLATORO </t>
+          <t xml:space="preserve">REBECA ABIGAIL VEGA FLORES </t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>854</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>CAJERO</t>
+          <t>CAJERO MOVIL</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA USULUTAN  </t>
+          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS MANUEL VALENCIA GUERRERO </t>
+          <t xml:space="preserve">SAMUEL ALBERTO SALGUERO RODRIGUEZ </t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>968</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>SUBJEFE DE  AGENCIA</t>
+          <t>CAJERO MOVIL</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA USULUTAN  </t>
+          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELVIN ELISEO HERNANDEZ MACHADO </t>
+          <t xml:space="preserve">SANDRA VERONICA ACEVEDO BELTRAN </t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>713</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>EJECUTIVO DE NEGOCIOS</t>
+          <t xml:space="preserve">ASISTENTE PARA CORRESPONSALES FINANCIEROS </t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA USULUTAN  </t>
+          <t xml:space="preserve">SUB GERENCIA DE CANALES </t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
     </row>
@@ -17132,14 +17122,6 @@
         </is>
       </c>
     </row>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30729,7 +30711,7 @@
       </c>
       <c r="D176" s="6" t="str">
         <f>'Base Oficial'!G176</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E176" s="6" t="str">
         <f>'Base Oficial'!D176</f>
@@ -30775,7 +30757,7 @@
       </c>
       <c r="D177" s="6" t="str">
         <f>'Base Oficial'!G177</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E177" s="6" t="str">
         <f>'Base Oficial'!D177</f>
@@ -30821,7 +30803,7 @@
       </c>
       <c r="D178" s="6" t="str">
         <f>'Base Oficial'!G178</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E178" s="6" t="str">
         <f>'Base Oficial'!D178</f>
@@ -30867,7 +30849,7 @@
       </c>
       <c r="D179" s="6" t="str">
         <f>'Base Oficial'!G179</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E179" s="6" t="str">
         <f>'Base Oficial'!D179</f>
@@ -30913,7 +30895,7 @@
       </c>
       <c r="D180" s="6" t="str">
         <f>'Base Oficial'!G180</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E180" s="6" t="str">
         <f>'Base Oficial'!D180</f>
@@ -30959,7 +30941,7 @@
       </c>
       <c r="D181" s="6" t="str">
         <f>'Base Oficial'!G181</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E181" s="6" t="str">
         <f>'Base Oficial'!D181</f>
@@ -31005,7 +30987,7 @@
       </c>
       <c r="D182" s="6" t="str">
         <f>'Base Oficial'!G182</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E182" s="6" t="str">
         <f>'Base Oficial'!D182</f>
@@ -31051,7 +31033,7 @@
       </c>
       <c r="D183" s="6" t="str">
         <f>'Base Oficial'!G183</f>
-        <v>Gerencia General</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E183" s="6" t="str">
         <f>'Base Oficial'!D183</f>
@@ -31419,7 +31401,7 @@
       </c>
       <c r="D191" s="6" t="str">
         <f>'Base Oficial'!G191</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E191" s="6" t="str">
         <f>'Base Oficial'!D191</f>
@@ -31465,7 +31447,7 @@
       </c>
       <c r="D192" s="6" t="str">
         <f>'Base Oficial'!G192</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E192" s="6" t="str">
         <f>'Base Oficial'!D192</f>
@@ -31511,7 +31493,7 @@
       </c>
       <c r="D193" s="6" t="str">
         <f>'Base Oficial'!G193</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E193" s="6" t="str">
         <f>'Base Oficial'!D193</f>
@@ -31557,7 +31539,7 @@
       </c>
       <c r="D194" s="6" t="str">
         <f>'Base Oficial'!G194</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E194" s="6" t="str">
         <f>'Base Oficial'!D194</f>
@@ -31603,7 +31585,7 @@
       </c>
       <c r="D195" s="6" t="str">
         <f>'Base Oficial'!G195</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E195" s="6" t="str">
         <f>'Base Oficial'!D195</f>
@@ -31649,7 +31631,7 @@
       </c>
       <c r="D196" s="6" t="str">
         <f>'Base Oficial'!G196</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E196" s="6" t="str">
         <f>'Base Oficial'!D196</f>
@@ -31695,7 +31677,7 @@
       </c>
       <c r="D197" s="6" t="str">
         <f>'Base Oficial'!G197</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E197" s="6" t="str">
         <f>'Base Oficial'!D197</f>
@@ -31741,7 +31723,7 @@
       </c>
       <c r="D198" s="6" t="str">
         <f>'Base Oficial'!G198</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E198" s="6" t="str">
         <f>'Base Oficial'!D198</f>
@@ -31787,7 +31769,7 @@
       </c>
       <c r="D199" s="6" t="str">
         <f>'Base Oficial'!G199</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E199" s="6" t="str">
         <f>'Base Oficial'!D199</f>
@@ -31833,7 +31815,7 @@
       </c>
       <c r="D200" s="6" t="str">
         <f>'Base Oficial'!G200</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E200" s="6" t="str">
         <f>'Base Oficial'!D200</f>
@@ -31879,7 +31861,7 @@
       </c>
       <c r="D201" s="6" t="str">
         <f>'Base Oficial'!G201</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E201" s="6" t="str">
         <f>'Base Oficial'!D201</f>
@@ -31925,7 +31907,7 @@
       </c>
       <c r="D202" s="6" t="str">
         <f>'Base Oficial'!G202</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E202" s="6" t="str">
         <f>'Base Oficial'!D202</f>
@@ -31971,7 +31953,7 @@
       </c>
       <c r="D203" s="6" t="str">
         <f>'Base Oficial'!G203</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E203" s="6" t="str">
         <f>'Base Oficial'!D203</f>
@@ -32017,7 +31999,7 @@
       </c>
       <c r="D204" s="6" t="str">
         <f>'Base Oficial'!G204</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E204" s="6" t="str">
         <f>'Base Oficial'!D204</f>
@@ -32063,7 +32045,7 @@
       </c>
       <c r="D205" s="6" t="str">
         <f>'Base Oficial'!G205</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E205" s="6" t="str">
         <f>'Base Oficial'!D205</f>
@@ -32109,7 +32091,7 @@
       </c>
       <c r="D206" s="6" t="str">
         <f>'Base Oficial'!G206</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E206" s="6" t="str">
         <f>'Base Oficial'!D206</f>
@@ -32155,7 +32137,7 @@
       </c>
       <c r="D207" s="6" t="str">
         <f>'Base Oficial'!G207</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E207" s="6" t="str">
         <f>'Base Oficial'!D207</f>
@@ -32201,7 +32183,7 @@
       </c>
       <c r="D208" s="6" t="str">
         <f>'Base Oficial'!G208</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E208" s="6" t="str">
         <f>'Base Oficial'!D208</f>
@@ -32247,7 +32229,7 @@
       </c>
       <c r="D209" s="6" t="str">
         <f>'Base Oficial'!G209</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E209" s="6" t="str">
         <f>'Base Oficial'!D209</f>
@@ -32293,7 +32275,7 @@
       </c>
       <c r="D210" s="6" t="str">
         <f>'Base Oficial'!G210</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E210" s="6" t="str">
         <f>'Base Oficial'!D210</f>
@@ -32339,7 +32321,7 @@
       </c>
       <c r="D211" s="6" t="str">
         <f>'Base Oficial'!G211</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E211" s="6" t="str">
         <f>'Base Oficial'!D211</f>
@@ -32385,7 +32367,7 @@
       </c>
       <c r="D212" s="6" t="str">
         <f>'Base Oficial'!G212</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E212" s="6" t="str">
         <f>'Base Oficial'!D212</f>
@@ -32431,7 +32413,7 @@
       </c>
       <c r="D213" s="6" t="str">
         <f>'Base Oficial'!G213</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E213" s="6" t="str">
         <f>'Base Oficial'!D213</f>
@@ -32477,7 +32459,7 @@
       </c>
       <c r="D214" s="6" t="str">
         <f>'Base Oficial'!G214</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E214" s="6" t="str">
         <f>'Base Oficial'!D214</f>
@@ -32523,7 +32505,7 @@
       </c>
       <c r="D215" s="6" t="str">
         <f>'Base Oficial'!G215</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E215" s="6" t="str">
         <f>'Base Oficial'!D215</f>
@@ -32569,7 +32551,7 @@
       </c>
       <c r="D216" s="6" t="str">
         <f>'Base Oficial'!G216</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E216" s="6" t="str">
         <f>'Base Oficial'!D216</f>
@@ -32615,7 +32597,7 @@
       </c>
       <c r="D217" s="6" t="str">
         <f>'Base Oficial'!G217</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E217" s="6" t="str">
         <f>'Base Oficial'!D217</f>
@@ -32661,7 +32643,7 @@
       </c>
       <c r="D218" s="6" t="str">
         <f>'Base Oficial'!G218</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E218" s="6" t="str">
         <f>'Base Oficial'!D218</f>
@@ -32707,7 +32689,7 @@
       </c>
       <c r="D219" s="6" t="str">
         <f>'Base Oficial'!G219</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E219" s="6" t="str">
         <f>'Base Oficial'!D219</f>
@@ -32753,7 +32735,7 @@
       </c>
       <c r="D220" s="6" t="str">
         <f>'Base Oficial'!G220</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E220" s="6" t="str">
         <f>'Base Oficial'!D220</f>
@@ -32799,7 +32781,7 @@
       </c>
       <c r="D221" s="6" t="str">
         <f>'Base Oficial'!G221</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E221" s="6" t="str">
         <f>'Base Oficial'!D221</f>
@@ -32845,7 +32827,7 @@
       </c>
       <c r="D222" s="6" t="str">
         <f>'Base Oficial'!G222</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E222" s="6" t="str">
         <f>'Base Oficial'!D222</f>
@@ -32891,7 +32873,7 @@
       </c>
       <c r="D223" s="6" t="str">
         <f>'Base Oficial'!G223</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E223" s="6" t="str">
         <f>'Base Oficial'!D223</f>
@@ -32937,7 +32919,7 @@
       </c>
       <c r="D224" s="6" t="str">
         <f>'Base Oficial'!G224</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E224" s="6" t="str">
         <f>'Base Oficial'!D224</f>
@@ -32983,7 +32965,7 @@
       </c>
       <c r="D225" s="6" t="str">
         <f>'Base Oficial'!G225</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E225" s="6" t="str">
         <f>'Base Oficial'!D225</f>
@@ -33029,7 +33011,7 @@
       </c>
       <c r="D226" s="6" t="str">
         <f>'Base Oficial'!G226</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E226" s="6" t="str">
         <f>'Base Oficial'!D226</f>
@@ -33075,7 +33057,7 @@
       </c>
       <c r="D227" s="6" t="str">
         <f>'Base Oficial'!G227</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E227" s="6" t="str">
         <f>'Base Oficial'!D227</f>
@@ -33121,7 +33103,7 @@
       </c>
       <c r="D228" s="6" t="str">
         <f>'Base Oficial'!G228</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E228" s="6" t="str">
         <f>'Base Oficial'!D228</f>
@@ -33167,7 +33149,7 @@
       </c>
       <c r="D229" s="6" t="str">
         <f>'Base Oficial'!G229</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E229" s="6" t="str">
         <f>'Base Oficial'!D229</f>
@@ -33213,7 +33195,7 @@
       </c>
       <c r="D230" s="6" t="str">
         <f>'Base Oficial'!G230</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E230" s="6" t="str">
         <f>'Base Oficial'!D230</f>
@@ -33259,7 +33241,7 @@
       </c>
       <c r="D231" s="6" t="str">
         <f>'Base Oficial'!G231</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E231" s="6" t="str">
         <f>'Base Oficial'!D231</f>
@@ -33305,7 +33287,7 @@
       </c>
       <c r="D232" s="6" t="str">
         <f>'Base Oficial'!G232</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E232" s="6" t="str">
         <f>'Base Oficial'!D232</f>
@@ -33351,7 +33333,7 @@
       </c>
       <c r="D233" s="6" t="str">
         <f>'Base Oficial'!G233</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E233" s="6" t="str">
         <f>'Base Oficial'!D233</f>
@@ -33397,7 +33379,7 @@
       </c>
       <c r="D234" s="6" t="str">
         <f>'Base Oficial'!G234</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E234" s="6" t="str">
         <f>'Base Oficial'!D234</f>
@@ -33443,7 +33425,7 @@
       </c>
       <c r="D235" s="6" t="str">
         <f>'Base Oficial'!G235</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E235" s="6" t="str">
         <f>'Base Oficial'!D235</f>
@@ -33489,7 +33471,7 @@
       </c>
       <c r="D236" s="6" t="str">
         <f>'Base Oficial'!G236</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E236" s="6" t="str">
         <f>'Base Oficial'!D236</f>
@@ -33535,7 +33517,7 @@
       </c>
       <c r="D237" s="6" t="str">
         <f>'Base Oficial'!G237</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E237" s="6" t="str">
         <f>'Base Oficial'!D237</f>
@@ -33581,7 +33563,7 @@
       </c>
       <c r="D238" s="6" t="str">
         <f>'Base Oficial'!G238</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E238" s="6" t="str">
         <f>'Base Oficial'!D238</f>
@@ -33627,7 +33609,7 @@
       </c>
       <c r="D239" s="6" t="str">
         <f>'Base Oficial'!G239</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E239" s="6" t="str">
         <f>'Base Oficial'!D239</f>
@@ -33673,7 +33655,7 @@
       </c>
       <c r="D240" s="6" t="str">
         <f>'Base Oficial'!G240</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E240" s="6" t="str">
         <f>'Base Oficial'!D240</f>
@@ -33719,7 +33701,7 @@
       </c>
       <c r="D241" s="6" t="str">
         <f>'Base Oficial'!G241</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E241" s="6" t="str">
         <f>'Base Oficial'!D241</f>
@@ -33765,7 +33747,7 @@
       </c>
       <c r="D242" s="6" t="str">
         <f>'Base Oficial'!G242</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E242" s="6" t="str">
         <f>'Base Oficial'!D242</f>
@@ -33811,7 +33793,7 @@
       </c>
       <c r="D243" s="6" t="str">
         <f>'Base Oficial'!G243</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E243" s="6" t="str">
         <f>'Base Oficial'!D243</f>
@@ -33857,7 +33839,7 @@
       </c>
       <c r="D244" s="6" t="str">
         <f>'Base Oficial'!G244</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E244" s="6" t="str">
         <f>'Base Oficial'!D244</f>
@@ -33903,7 +33885,7 @@
       </c>
       <c r="D245" s="6" t="str">
         <f>'Base Oficial'!G245</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E245" s="6" t="str">
         <f>'Base Oficial'!D245</f>
@@ -33949,7 +33931,7 @@
       </c>
       <c r="D246" s="6" t="str">
         <f>'Base Oficial'!G246</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E246" s="6" t="str">
         <f>'Base Oficial'!D246</f>
@@ -33995,7 +33977,7 @@
       </c>
       <c r="D247" s="6" t="str">
         <f>'Base Oficial'!G247</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E247" s="6" t="str">
         <f>'Base Oficial'!D247</f>
@@ -34041,7 +34023,7 @@
       </c>
       <c r="D248" s="6" t="str">
         <f>'Base Oficial'!G248</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E248" s="6" t="str">
         <f>'Base Oficial'!D248</f>
@@ -34087,7 +34069,7 @@
       </c>
       <c r="D249" s="6" t="str">
         <f>'Base Oficial'!G249</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E249" s="6" t="str">
         <f>'Base Oficial'!D249</f>
@@ -34133,7 +34115,7 @@
       </c>
       <c r="D250" s="6" t="str">
         <f>'Base Oficial'!G250</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E250" s="6" t="str">
         <f>'Base Oficial'!D250</f>
@@ -34179,7 +34161,7 @@
       </c>
       <c r="D251" s="6" t="str">
         <f>'Base Oficial'!G251</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E251" s="6" t="str">
         <f>'Base Oficial'!D251</f>
@@ -34225,7 +34207,7 @@
       </c>
       <c r="D252" s="6" t="str">
         <f>'Base Oficial'!G252</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E252" s="6" t="str">
         <f>'Base Oficial'!D252</f>
@@ -34271,7 +34253,7 @@
       </c>
       <c r="D253" s="6" t="str">
         <f>'Base Oficial'!G253</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E253" s="6" t="str">
         <f>'Base Oficial'!D253</f>
@@ -34317,7 +34299,7 @@
       </c>
       <c r="D254" s="6" t="str">
         <f>'Base Oficial'!G254</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E254" s="6" t="str">
         <f>'Base Oficial'!D254</f>
@@ -34363,7 +34345,7 @@
       </c>
       <c r="D255" s="6" t="str">
         <f>'Base Oficial'!G255</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E255" s="6" t="str">
         <f>'Base Oficial'!D255</f>
@@ -34409,7 +34391,7 @@
       </c>
       <c r="D256" s="6" t="str">
         <f>'Base Oficial'!G256</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E256" s="6" t="str">
         <f>'Base Oficial'!D256</f>
@@ -34455,7 +34437,7 @@
       </c>
       <c r="D257" s="6" t="str">
         <f>'Base Oficial'!G257</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E257" s="6" t="str">
         <f>'Base Oficial'!D257</f>
@@ -34501,7 +34483,7 @@
       </c>
       <c r="D258" s="6" t="str">
         <f>'Base Oficial'!G258</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E258" s="6" t="str">
         <f>'Base Oficial'!D258</f>
@@ -34547,7 +34529,7 @@
       </c>
       <c r="D259" s="6" t="str">
         <f>'Base Oficial'!G259</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E259" s="6" t="str">
         <f>'Base Oficial'!D259</f>
@@ -34593,7 +34575,7 @@
       </c>
       <c r="D260" s="6" t="str">
         <f>'Base Oficial'!G260</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E260" s="6" t="str">
         <f>'Base Oficial'!D260</f>
@@ -34639,7 +34621,7 @@
       </c>
       <c r="D261" s="6" t="str">
         <f>'Base Oficial'!G261</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E261" s="6" t="str">
         <f>'Base Oficial'!D261</f>
@@ -34685,7 +34667,7 @@
       </c>
       <c r="D262" s="6" t="str">
         <f>'Base Oficial'!G262</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E262" s="6" t="str">
         <f>'Base Oficial'!D262</f>
@@ -34731,7 +34713,7 @@
       </c>
       <c r="D263" s="6" t="str">
         <f>'Base Oficial'!G263</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E263" s="6" t="str">
         <f>'Base Oficial'!D263</f>
@@ -34777,7 +34759,7 @@
       </c>
       <c r="D264" s="6" t="str">
         <f>'Base Oficial'!G264</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E264" s="6" t="str">
         <f>'Base Oficial'!D264</f>
@@ -34823,7 +34805,7 @@
       </c>
       <c r="D265" s="6" t="str">
         <f>'Base Oficial'!G265</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E265" s="6" t="str">
         <f>'Base Oficial'!D265</f>
@@ -34869,7 +34851,7 @@
       </c>
       <c r="D266" s="6" t="str">
         <f>'Base Oficial'!G266</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E266" s="6" t="str">
         <f>'Base Oficial'!D266</f>
@@ -34915,7 +34897,7 @@
       </c>
       <c r="D267" s="6" t="str">
         <f>'Base Oficial'!G267</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E267" s="6" t="str">
         <f>'Base Oficial'!D267</f>
@@ -34961,7 +34943,7 @@
       </c>
       <c r="D268" s="6" t="str">
         <f>'Base Oficial'!G268</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E268" s="6" t="str">
         <f>'Base Oficial'!D268</f>
@@ -35007,7 +34989,7 @@
       </c>
       <c r="D269" s="6" t="str">
         <f>'Base Oficial'!G269</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E269" s="6" t="str">
         <f>'Base Oficial'!D269</f>
@@ -35053,7 +35035,7 @@
       </c>
       <c r="D270" s="6" t="str">
         <f>'Base Oficial'!G270</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E270" s="6" t="str">
         <f>'Base Oficial'!D270</f>
@@ -35099,7 +35081,7 @@
       </c>
       <c r="D271" s="6" t="str">
         <f>'Base Oficial'!G271</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E271" s="6" t="str">
         <f>'Base Oficial'!D271</f>
@@ -35145,7 +35127,7 @@
       </c>
       <c r="D272" s="6" t="str">
         <f>'Base Oficial'!G272</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E272" s="6" t="str">
         <f>'Base Oficial'!D272</f>
@@ -35191,7 +35173,7 @@
       </c>
       <c r="D273" s="6" t="str">
         <f>'Base Oficial'!G273</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E273" s="6" t="str">
         <f>'Base Oficial'!D273</f>
@@ -35237,7 +35219,7 @@
       </c>
       <c r="D274" s="6" t="str">
         <f>'Base Oficial'!G274</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E274" s="6" t="str">
         <f>'Base Oficial'!D274</f>
@@ -35283,7 +35265,7 @@
       </c>
       <c r="D275" s="6" t="str">
         <f>'Base Oficial'!G275</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E275" s="6" t="str">
         <f>'Base Oficial'!D275</f>
@@ -35329,7 +35311,7 @@
       </c>
       <c r="D276" s="6" t="str">
         <f>'Base Oficial'!G276</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E276" s="6" t="str">
         <f>'Base Oficial'!D276</f>
@@ -35375,7 +35357,7 @@
       </c>
       <c r="D277" s="6" t="str">
         <f>'Base Oficial'!G277</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E277" s="6" t="str">
         <f>'Base Oficial'!D277</f>
@@ -35421,7 +35403,7 @@
       </c>
       <c r="D278" s="6" t="str">
         <f>'Base Oficial'!G278</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E278" s="6" t="str">
         <f>'Base Oficial'!D278</f>
@@ -35467,7 +35449,7 @@
       </c>
       <c r="D279" s="6" t="str">
         <f>'Base Oficial'!G279</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E279" s="6" t="str">
         <f>'Base Oficial'!D279</f>
@@ -35513,7 +35495,7 @@
       </c>
       <c r="D280" s="6" t="str">
         <f>'Base Oficial'!G280</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E280" s="6" t="str">
         <f>'Base Oficial'!D280</f>
@@ -35559,7 +35541,7 @@
       </c>
       <c r="D281" s="6" t="str">
         <f>'Base Oficial'!G281</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E281" s="6" t="str">
         <f>'Base Oficial'!D281</f>
@@ -35605,7 +35587,7 @@
       </c>
       <c r="D282" s="6" t="str">
         <f>'Base Oficial'!G282</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E282" s="6" t="str">
         <f>'Base Oficial'!D282</f>
@@ -35651,7 +35633,7 @@
       </c>
       <c r="D283" s="6" t="str">
         <f>'Base Oficial'!G283</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E283" s="6" t="str">
         <f>'Base Oficial'!D283</f>
@@ -35697,7 +35679,7 @@
       </c>
       <c r="D284" s="6" t="str">
         <f>'Base Oficial'!G284</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E284" s="6" t="str">
         <f>'Base Oficial'!D284</f>
@@ -35743,7 +35725,7 @@
       </c>
       <c r="D285" s="6" t="str">
         <f>'Base Oficial'!G285</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E285" s="6" t="str">
         <f>'Base Oficial'!D285</f>
@@ -35789,7 +35771,7 @@
       </c>
       <c r="D286" s="6" t="str">
         <f>'Base Oficial'!G286</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E286" s="6" t="str">
         <f>'Base Oficial'!D286</f>
@@ -35835,7 +35817,7 @@
       </c>
       <c r="D287" s="6" t="str">
         <f>'Base Oficial'!G287</f>
-        <v>Gerencia de Negocios (Agencias)</v>
+        <v>Gerencia de Negocios</v>
       </c>
       <c r="E287" s="6" t="str">
         <f>'Base Oficial'!D287</f>
@@ -36538,7 +36520,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C8" s="8">
@@ -36598,7 +36580,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C9" s="8">
@@ -36658,7 +36640,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C10" s="8">
@@ -36718,7 +36700,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C11" s="8">
@@ -36778,7 +36760,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C12" s="8">
@@ -36838,7 +36820,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C13" s="8">
@@ -36898,7 +36880,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C14" s="8">
@@ -36958,7 +36940,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C15" s="8">
@@ -37018,7 +37000,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C16" s="8">
@@ -37138,7 +37120,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Gerencia General</t>
+          <t>Gerencia de Negocios</t>
         </is>
       </c>
       <c r="C18" s="8">
@@ -38941,7 +38923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -39158,19 +39140,19 @@
       </c>
       <c r="B7" s="8">
         <f>COUNTIF('Detalle individual'!$D$5:$D$295, A7)</f>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8">
         <f>COUNTIFS('Detalle individual'!$D$5:$D$295, A7, 'Detalle individual'!$F$5:$F$295, "Completado")</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D7" s="8">
         <f>B7-C7</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" s="9">
         <f>IF(B7&gt;0, C7/B7, 0)</f>
-        <v>0.761904761904762</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F7" s="4" t="str">
         <f>IF(AND(B7&gt;0, C7=B7), "Completo", "Pendiente")</f>
@@ -39178,7 +39160,7 @@
       </c>
       <c r="G7" s="7">
         <f>IF(C7&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A7), ""), "")</f>
-        <v>96.25</v>
+        <v>98.75</v>
       </c>
       <c r="H7" s="6">
         <f>IF(C7&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A7), ""), "")</f>
@@ -39186,7 +39168,7 @@
       </c>
       <c r="I7" s="6">
         <f>IF(C7&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A7), ""), "")</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J7" s="25">
         <f>IF(C7&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$G$5:$G$295, 'Detalle individual'!$D$5:$D$295, A7), ""), "")</f>
@@ -39202,7 +39184,7 @@
       </c>
       <c r="M7" s="7">
         <f>IF(C7&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A7), ""), "")</f>
-        <v>8.015625</v>
+        <v>7.65416666666667</v>
       </c>
     </row>
     <row r="8">
@@ -39323,19 +39305,19 @@
       </c>
       <c r="B10" s="8">
         <f>COUNTIF('Detalle individual'!$D$5:$D$295, A10)</f>
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="C10" s="8">
         <f>COUNTIFS('Detalle individual'!$D$5:$D$295, A10, 'Detalle individual'!$F$5:$F$295, "Completado")</f>
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D10" s="8">
         <f>B10-C10</f>
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="E10" s="9">
         <f>IF(B10&gt;0, C10/B10, 0)</f>
-        <v>0.39344262295082</v>
+        <v>0.391566265060241</v>
       </c>
       <c r="F10" s="4" t="str">
         <f>IF(AND(B10&gt;0, C10=B10), "Completo", "Pendiente")</f>
@@ -39343,7 +39325,7 @@
       </c>
       <c r="G10" s="7">
         <f>IF(C10&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A10), ""), "")</f>
-        <v>97.5</v>
+        <v>96.5384615384615</v>
       </c>
       <c r="H10" s="6">
         <f>IF(C10&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A10), ""), "")</f>
@@ -39351,7 +39333,7 @@
       </c>
       <c r="I10" s="6">
         <f>IF(C10&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A10), ""), "")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J10" s="25">
         <f>IF(C10&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$G$5:$G$295, 'Detalle individual'!$D$5:$D$295, A10), ""), "")</f>
@@ -39363,42 +39345,42 @@
       </c>
       <c r="L10" s="7">
         <f>IF(C10&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A10), ""), "")</f>
-        <v>3.03333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="M10" s="7">
         <f>IF(C10&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A10), ""), "")</f>
-        <v>13.8222222230333</v>
+        <v>14.2371794872797</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
+          <t>Gerencia de Oficialía de Cumplimiento</t>
         </is>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF('Detalle individual'!$D$5:$D$295, A11)</f>
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="C11" s="8">
         <f>COUNTIFS('Detalle individual'!$D$5:$D$295, A11, 'Detalle individual'!$F$5:$F$295, "Completado")</f>
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D11" s="8">
         <f>B11-C11</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E11" s="9">
         <f>IF(B11&gt;0, C11/B11, 0)</f>
-        <v>0.381443298969072</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="str">
         <f>IF(AND(B11&gt;0, C11=B11), "Completo", "Pendiente")</f>
-        <v>Pendiente</v>
+        <v>Completo</v>
       </c>
       <c r="G11" s="7">
         <f>IF(C11&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
-        <v>96.7567567567568</v>
+        <v>100</v>
       </c>
       <c r="H11" s="6">
         <f>IF(C11&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
@@ -39406,54 +39388,54 @@
       </c>
       <c r="I11" s="6">
         <f>IF(C11&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J11" s="25">
         <f>IF(C11&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$G$5:$G$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
-        <v>46296.43491898148</v>
+        <v>46296.47011574074</v>
       </c>
       <c r="K11" s="25">
         <f>IF(C11&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$H$5:$H$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
-        <v>46305.407002314816</v>
+        <v>46296.49747685185</v>
       </c>
       <c r="L11" s="7">
         <f>IF(C11&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
-        <v>1.75</v>
+        <v>9.16666666666667</v>
       </c>
       <c r="M11" s="7">
         <f>IF(C11&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A11), ""), "")</f>
-        <v>15.0617117113617</v>
+        <v>11.9642857142857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Oficialía de Cumplimiento</t>
+          <t>Gerencia de Operaciones</t>
         </is>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF('Detalle individual'!$D$5:$D$295, A12)</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C12" s="8">
         <f>COUNTIFS('Detalle individual'!$D$5:$D$295, A12, 'Detalle individual'!$F$5:$F$295, "Completado")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="8">
         <f>B12-C12</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E12" s="9">
         <f>IF(B12&gt;0, C12/B12, 0)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="4" t="str">
         <f>IF(AND(B12&gt;0, C12=B12), "Completo", "Pendiente")</f>
-        <v>Completo</v>
+        <v>Pendiente</v>
       </c>
       <c r="G12" s="7">
         <f>IF(C12&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="H12" s="6">
         <f>IF(C12&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
@@ -39461,46 +39443,46 @@
       </c>
       <c r="I12" s="6">
         <f>IF(C12&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J12" s="25">
         <f>IF(C12&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$G$5:$G$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
-        <v>46296.47011574074</v>
+        <v>46296.56951388889</v>
       </c>
       <c r="K12" s="25">
         <f>IF(C12&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$H$5:$H$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
-        <v>46296.49747685185</v>
+        <v>46304.692928240744</v>
       </c>
       <c r="L12" s="7">
         <f>IF(C12&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
-        <v>9.16666666666667</v>
+        <v>1.68333333333333</v>
       </c>
       <c r="M12" s="7">
         <f>IF(C12&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A12), ""), "")</f>
-        <v>11.9642857142857</v>
+        <v>10.025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Operaciones</t>
+          <t>Gerencia de Sistemas</t>
         </is>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF('Detalle individual'!$D$5:$D$295, A13)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C13" s="8">
         <f>COUNTIFS('Detalle individual'!$D$5:$D$295, A13, 'Detalle individual'!$F$5:$F$295, "Completado")</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D13" s="8">
         <f>B13-C13</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="9">
         <f>IF(B13&gt;0, C13/B13, 0)</f>
-        <v>0.5</v>
+        <v>0.739130434782609</v>
       </c>
       <c r="F13" s="4" t="str">
         <f>IF(AND(B13&gt;0, C13=B13), "Completo", "Pendiente")</f>
@@ -39508,7 +39490,7 @@
       </c>
       <c r="G13" s="7">
         <f>IF(C13&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A13), ""), "")</f>
-        <v>98.75</v>
+        <v>99.4117647058824</v>
       </c>
       <c r="H13" s="6">
         <f>IF(C13&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A13), ""), "")</f>
@@ -39520,73 +39502,18 @@
       </c>
       <c r="J13" s="25">
         <f>IF(C13&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$G$5:$G$295, 'Detalle individual'!$D$5:$D$295, A13), ""), "")</f>
-        <v>46296.56951388889</v>
+        <v>46296.56962962963</v>
       </c>
       <c r="K13" s="25">
         <f>IF(C13&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$H$5:$H$295, 'Detalle individual'!$D$5:$D$295, A13), ""), "")</f>
-        <v>46304.692928240744</v>
+        <v>46304.407905092594</v>
       </c>
       <c r="L13" s="7">
         <f>IF(C13&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A13), ""), "")</f>
-        <v>1.68333333333333</v>
+        <v>3.16666666666667</v>
       </c>
       <c r="M13" s="7">
         <f>IF(C13&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A13), ""), "")</f>
-        <v>10.025</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Gerencia de Sistemas</t>
-        </is>
-      </c>
-      <c r="B14" s="8">
-        <f>COUNTIF('Detalle individual'!$D$5:$D$295, A14)</f>
-        <v>23</v>
-      </c>
-      <c r="C14" s="8">
-        <f>COUNTIFS('Detalle individual'!$D$5:$D$295, A14, 'Detalle individual'!$F$5:$F$295, "Completado")</f>
-        <v>17</v>
-      </c>
-      <c r="D14" s="8">
-        <f>B14-C14</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="9">
-        <f>IF(B14&gt;0, C14/B14, 0)</f>
-        <v>0.739130434782609</v>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f>IF(AND(B14&gt;0, C14=B14), "Completo", "Pendiente")</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="G14" s="7">
-        <f>IF(C14&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
-        <v>99.4117647058824</v>
-      </c>
-      <c r="H14" s="6">
-        <f>IF(C14&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
-        <v>100</v>
-      </c>
-      <c r="I14" s="6">
-        <f>IF(C14&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$J$5:$J$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
-        <v>95</v>
-      </c>
-      <c r="J14" s="25">
-        <f>IF(C14&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$G$5:$G$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
-        <v>46296.56962962963</v>
-      </c>
-      <c r="K14" s="25">
-        <f>IF(C14&gt;0, IFERROR(_xlfn.MAXIFS('Detalle individual'!$H$5:$H$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
-        <v>46304.407905092594</v>
-      </c>
-      <c r="L14" s="7">
-        <f>IF(C14&gt;0, IFERROR(_xlfn.MINIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
-        <v>3.16666666666667</v>
-      </c>
-      <c r="M14" s="7">
-        <f>IF(C14&gt;0, IFERROR(AVERAGEIFS('Detalle individual'!$I$5:$I$295, 'Detalle individual'!$D$5:$D$295, A14), ""), "")</f>
         <v>14.8254901960784</v>
       </c>
     </row>
@@ -39779,7 +39706,7 @@
           <t>Gerencia General</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr"/>
+      <c r="B7" s="11" t="n"/>
       <c r="D7" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B7, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A7, "")</f>
         <v/>
@@ -39823,7 +39750,7 @@
           <t>Gerencia Legal y Cumplimiento Normativo</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr"/>
+      <c r="B8" s="11" t="n"/>
       <c r="D8" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B8, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A8, "")</f>
         <v/>
@@ -39867,7 +39794,7 @@
           <t>Gerencia de Finanzas y Planificación</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr"/>
+      <c r="B9" s="11" t="n"/>
       <c r="D9" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B9, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A9, "")</f>
         <v/>
@@ -39911,7 +39838,7 @@
           <t>Gerencia de Negocios</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
+      <c r="B10" s="11" t="n"/>
       <c r="D10" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B10, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A10, "")</f>
         <v/>
@@ -39952,10 +39879,10 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Negocios (Agencias)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr"/>
+          <t>Gerencia de Oficialía de Cumplimiento</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
       <c r="D11" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B11, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A11, "")</f>
         <v/>
@@ -39996,10 +39923,10 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Oficialía de Cumplimiento</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr"/>
+          <t>Gerencia de Operaciones</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n"/>
       <c r="D12" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B12, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A12, "")</f>
         <v/>
@@ -40040,10 +39967,10 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Gerencia de Operaciones</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr"/>
+          <t>Gerencia de Sistemas</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n"/>
       <c r="D13" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B13, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A13, "")</f>
         <v/>
@@ -40082,12 +40009,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Gerencia de Sistemas</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr"/>
       <c r="D14" s="5" t="str">
         <f>IF(SUMIF($A$5:$A$14, 'Consolidado por área'!B14, $B$5:$B$14)&gt;=1, 'Consolidado por área'!A14, "")</f>
         <v/>
@@ -41466,11 +41387,11 @@
     </row>
     <row r="5">
       <c r="A5" s="15">
-        <f>SUM('Consolidado por Gerencia'!$B$5:$B$14)</f>
+        <f>SUM('Consolidado por Gerencia'!$B$5:$B$13)</f>
         <v>291</v>
       </c>
       <c r="D5" s="16">
-        <f>SUM('Consolidado por Gerencia'!$C$5:$C$14)</f>
+        <f>SUM('Consolidado por Gerencia'!$C$5:$C$13)</f>
         <v>154</v>
       </c>
       <c r="E5" s="20" t="n"/>
